--- a/Excel/01_Financial_Dashboard.xlsx
+++ b/Excel/01_Financial_Dashboard.xlsx
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="8">
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>196.1</v>
+        <v>195.5</v>
       </c>
     </row>
     <row r="9">
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>89.09999999999999</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -772,7 +772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -986,30 +986,86 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B10" s="2" t="n">
         <v>220</v>
       </c>
-      <c r="C8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="2" t="n">
+      <c r="C10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2" t="n">
         <v>22.1</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E10" s="2" t="n">
         <v>0.01</v>
       </c>
-      <c r="F8" s="2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>196.1</v>
-      </c>
-      <c r="H8" s="2" t="n">
+      <c r="F10" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>195.5</v>
+      </c>
+      <c r="H10" s="2" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1052,7 +1108,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1068,7 +1124,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1084,33 +1140,33 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="C4" t="n">
-        <v>-2.11</v>
+        <v>195.79</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>195.8</v>
+        <v>-2.1</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/01_Financial_Dashboard.xlsx
+++ b/Excel/01_Financial_Dashboard.xlsx
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="8">
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>195.5</v>
+        <v>193.4</v>
       </c>
     </row>
     <row r="9">
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>88.90000000000001</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -772,7 +772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1042,30 +1042,226 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B17" s="2" t="n">
         <v>220</v>
       </c>
-      <c r="C10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="2" t="n">
+      <c r="C17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="2" t="n">
         <v>22.1</v>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E17" s="2" t="n">
         <v>0.01</v>
       </c>
-      <c r="F10" s="2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>195.5</v>
-      </c>
-      <c r="H10" s="2" t="n">
+      <c r="F17" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>193.4</v>
+      </c>
+      <c r="H17" s="2" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1108,7 +1304,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1124,39 +1320,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="C3" t="n">
-        <v>-2.1</v>
+        <v>195.79</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>195.79</v>
+        <v>-2.1</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B5" t="n">

--- a/Excel/01_Financial_Dashboard.xlsx
+++ b/Excel/01_Financial_Dashboard.xlsx
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>220</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="8">
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>193.4</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="9">
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>87.90000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -772,7 +772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -820,17 +820,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>22.1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -839,430 +839,38 @@
         <v>0.3</v>
       </c>
       <c r="G2" t="n">
-        <v>197.6</v>
+        <v>-0.3</v>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="F3" t="n">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="n">
         <v>0.3</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="2" t="n">
         <v>-0.3</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G13" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>220</v>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>193.4</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>6</v>
+      <c r="H3" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1304,7 +912,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1320,23 +928,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>195.79</v>
+        <v>-2.1</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1352,7 +960,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B5" t="n">

--- a/Excel/01_Financial_Dashboard.xlsx
+++ b/Excel/01_Financial_Dashboard.xlsx
@@ -820,7 +820,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -912,7 +912,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -928,7 +928,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -944,7 +944,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -960,7 +960,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B5" t="n">

--- a/Excel/01_Financial_Dashboard.xlsx
+++ b/Excel/01_Financial_Dashboard.xlsx
@@ -820,7 +820,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -912,7 +912,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -928,7 +928,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -944,7 +944,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -960,7 +960,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B5" t="n">

--- a/Excel/01_Financial_Dashboard.xlsx
+++ b/Excel/01_Financial_Dashboard.xlsx
@@ -820,7 +820,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -912,7 +912,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -928,7 +928,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -944,7 +944,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -960,7 +960,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">

--- a/Excel/01_Financial_Dashboard.xlsx
+++ b/Excel/01_Financial_Dashboard.xlsx
@@ -820,7 +820,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -912,7 +912,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -928,7 +928,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -944,7 +944,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -960,7 +960,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B5" t="n">

--- a/Excel/01_Financial_Dashboard.xlsx
+++ b/Excel/01_Financial_Dashboard.xlsx
@@ -820,7 +820,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -912,7 +912,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -928,7 +928,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -944,7 +944,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -960,7 +960,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B5" t="n">

--- a/Excel/01_Financial_Dashboard.xlsx
+++ b/Excel/01_Financial_Dashboard.xlsx
@@ -820,7 +820,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -912,7 +912,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -928,7 +928,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -944,7 +944,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -960,7 +960,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B5" t="n">

--- a/Excel/01_Financial_Dashboard.xlsx
+++ b/Excel/01_Financial_Dashboard.xlsx
@@ -820,7 +820,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -912,7 +912,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -928,7 +928,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -944,7 +944,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -960,7 +960,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B5" t="n">

--- a/Excel/01_Financial_Dashboard.xlsx
+++ b/Excel/01_Financial_Dashboard.xlsx
@@ -820,7 +820,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -912,7 +912,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -928,7 +928,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -944,7 +944,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -960,7 +960,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B5" t="n">
